--- a/data/Guillen2021/mmc3.xlsx
+++ b/data/Guillen2021/mmc3.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/notom/Dropbox (UMass Medical School)/Shared goods/Revision/sup information/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idunmariaburgos/SteadierCom/case_studies/data/Guillen2021/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE39ECF-4E28-C74C-9155-53FA88227F48}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8216C7B5-C74E-EB4B-976B-C0C005E3BA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="460" windowWidth="27640" windowHeight="16540" xr2:uid="{7FD5C330-153D-204A-900B-2411BE045A30}"/>
+    <workbookView xWindow="20520" yWindow="29300" windowWidth="27640" windowHeight="16300" activeTab="1" xr2:uid="{7FD5C330-153D-204A-900B-2411BE045A30}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="original" sheetId="1" r:id="rId1"/>
+    <sheet name="annotated" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -355,6 +356,9 @@
   </si>
   <si>
     <t>other</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
 </sst>
 </file>
@@ -469,30 +473,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -524,9 +521,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -564,7 +561,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -670,7 +667,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -812,7 +809,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -823,1486 +820,1485 @@
   <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>5.7253359108645901E-2</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>0.52516496989354999</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="2">
         <v>2.24929761450317</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>3.4697807442243298</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>8.1429695150761996E-2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>0.60490157308246995</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>1.6886639795354199</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>2.9845627606538501</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="12" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>0.99946360837134696</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>0.77745997716242099</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>2.5419496831137902</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>3.2262975559712901</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>-1.04291000429798</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>7.1930041399868805E-2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>0.85389986374818605</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>3.2679850441245102</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="14" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>0.46266505598100799</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>1.37483296515001</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>1.22986487908687</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>3.4153402051758399</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>0.81677909389428505</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>1.20560836043006</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>5.0051498803205297</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>4.7951641832852099</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>-0.63148277808465603</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>0.95741118225007604</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>1.0941989010290301</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>2.5299417952127699</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>-0.147259746094942</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>1.54681034415286</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>3.6915727544231798</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>4.4310069529560696</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>-0.17600466187914199</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>0.80679121388953001</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>1.20103238798944</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>2.51618194354243</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>0.83472783677895002</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>2.3142532627301402</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>3.05331309126157</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>4.5008987145633403</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>1.9424194382232001</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>2.5814847384597099</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>3.9352173599127598</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>4.9889332808810698</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>0.21471812451016301</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <v>2.0807726964733999</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="2">
         <v>2.8742512558578599</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>4.0803166420560499</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>0.44551197118126901</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>1.80408546308864</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
         <v>3.94626753061373</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>4.8641054511645399</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>-0.17302735564309499</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>0.41499280854753801</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>2.62735389434041</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>2.7027256254081302</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>0.26292781381798302</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>1.3365809084040601</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>4.9090970352420502</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>4.8992612387091796</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>0.11799404555833699</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>0.69347991058783398</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>4.91228877204773</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>4.7647152388466498</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>0.38181883589036097</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>-0.32070987888505498</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>4.1340126347495197E-2</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>3.1012628478968298</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>6.2165583289927599E-2</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>0.70074894585104996</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>1.5939051575351699</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>1.6794884965625301</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>0.24061880836111199</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>0.51965657337954596</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>1.22629228662599</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>1.9050735702263899</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>1.4382818030690001</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>0.44126964116772199</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>1.4114377385338801</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>3.0206273637232899</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>-0.68094920181181795</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>1.0579004407347601</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>2.1334004333424699</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>2.15797341137527</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>-0.52477561791105898</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>-0.53795559433433005</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>3.2449281121001401</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>2.2889898588425499</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>-0.58070263498933705</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>-1.07627076708953</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="2">
         <v>2.6194970493189</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>2.4818049458539799</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>7.6324465345508505E-2</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>0.69967712925408299</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="2">
         <v>3.3986016145907598</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>2.9766525969585702</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>-0.88500945706477396</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>-0.59537474777126298</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
         <v>0.97840990712292897</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>2.0231970714324401</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>0.23367351467366099</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>1.3784933954045899</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>0.670022471366435</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>1.6237261735499899</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>0.95868104715732605</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>1.26140559053955</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
         <v>1.7218613784939301</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>3.5399905367910498</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>1.6777235470412499</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>0.48020625655039001</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>3.5945831679224001</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>4.1460597495834302</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="6">
         <v>-0.17470308019642899</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="6">
         <v>-1.3496833066004501</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="6">
         <v>0.77610050167806299</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="6">
         <v>4.6225631169268704</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="6">
         <v>-0.25952874500900103</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="6">
         <v>-0.23917215799196001</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="6">
         <v>0.79570048239305902</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="6">
         <v>3.58215921017637</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="6">
         <v>2.5496643383684199</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="6">
         <v>3.5501853094266802</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="6">
         <v>3.0061668969144399</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="6">
         <v>6.65699781171387</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="6">
         <v>-1.4715574654065799</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="6">
         <v>0.366842182670641</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="6">
         <v>0.21683590696799901</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="6">
         <v>3.4763484360661998</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="6">
         <v>-1.8668259599516299</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="6">
         <v>-3.0000520658822198</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="6">
         <v>1.85955333155873</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="6">
         <v>4.2846380077877502</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="6">
         <v>0.151497944057881</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="6">
         <v>0.52802361383061103</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="6">
         <v>2.1193517176494798</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="6">
         <v>5.7012895993501997</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="6">
         <v>-2.70365404821499</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="6">
         <v>0.55345011325189097</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="6">
         <v>1.4718474308507501</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="6">
         <v>4.0196770114815497</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <v>0.27896212783503299</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="6">
         <v>0.69878389659691498</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="6">
         <v>1.04923338740626</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="6">
         <v>2.6082488130885202</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="9" t="s">
+      <c r="A38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <v>-2.1581401998371699</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="6">
         <v>0.63610322679327302</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="6">
         <v>2.4041021659485602</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="6">
         <v>4.8700243505413301</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <v>1.9835460998122601E-2</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="6">
         <v>-0.17484652643718299</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="6">
         <v>0.27875429368347598</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="6">
         <v>3.7718326609456101</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="6">
         <v>-9.5241129674304106E-2</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="6">
         <v>0.30847453185176998</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="6">
         <v>2.7244341507433201</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="6">
         <v>5.0452006559446598</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="6">
         <v>1.28862206451828</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="6">
         <v>0.99086777585602503</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="6">
         <v>2.6947511238309301</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="6">
         <v>4.6629604172764898</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="16">
         <v>2.9318541707430699</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="16">
         <v>3.3562382340177499</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="16">
         <v>3.1134395686573502</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="16">
         <v>6.0255594813580604</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="4">
         <v>0.13816050540685201</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="4">
         <v>0.957126529415254</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="4">
         <v>5.7191110657741202</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="4">
         <v>5.6894296721296103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="4">
         <v>-0.78939810576672897</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="4">
         <v>-6.8804548839318094E-2</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="4">
         <v>3.5924459853482298</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="4">
         <v>3.3884898247139899</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="4">
         <v>0.64825917362285801</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="4">
         <v>0.82831046474174597</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="4">
         <v>3.3072400467879999</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="4">
         <v>3.65783199211416</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="4">
         <v>9.0937851882498102E-2</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="4">
         <v>0.12016284988355801</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="4">
         <v>1.5466531539884401</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="4">
         <v>1.63380058879395</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="4">
         <v>-2.28271754669034</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="4">
         <v>-1.1700974664702299</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="4">
         <v>2.24340472198497</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="4">
         <v>2.7593948142789202</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="4">
         <v>-1.57401767908274</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="4">
         <v>3.2680352543495399</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="4">
         <v>2.57345176348392</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="4">
         <v>5.3373246798262297</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="9">
         <v>-0.27418919665039698</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="9">
         <v>1.23679237459143</v>
       </c>
-      <c r="E49" s="14">
+      <c r="E49" s="9">
         <v>1.9455827984601901</v>
       </c>
-      <c r="F49" s="14">
+      <c r="F49" s="9">
         <v>1.70933273154503</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="9">
         <v>6.1055263070113198E-2</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="9">
         <v>0.87235029628077698</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="9">
         <v>1.84719849936625</v>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="9">
         <v>1.7537822445416</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="9">
         <v>-0.72005248140336298</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="9">
         <v>0.97059539239316905</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="9">
         <v>1.7382880005360399</v>
       </c>
-      <c r="F51" s="14">
+      <c r="F51" s="9">
         <v>1.43097751978594</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="9">
         <v>-0.71439789052036995</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="9">
         <v>0.93876692094027603</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E52" s="9">
         <v>1.8018269024068201</v>
       </c>
-      <c r="F52" s="14">
+      <c r="F52" s="9">
         <v>1.3916371374796701</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="9">
         <v>-0.27742434353788697</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="9">
         <v>0.89386022566505396</v>
       </c>
-      <c r="E53" s="14">
+      <c r="E53" s="9">
         <v>2.07946584294874</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="9">
         <v>2.0734240816263401</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="9">
         <v>0.61234557615111396</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="9">
         <v>0.852530005332369</v>
       </c>
-      <c r="E54" s="14">
+      <c r="E54" s="9">
         <v>1.50388761609286</v>
       </c>
-      <c r="F54" s="14">
+      <c r="F54" s="9">
         <v>2.3815623344454102</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="9">
         <v>-0.13428677014482401</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="9">
         <v>9.3052269679316305E-2</v>
       </c>
-      <c r="E55" s="14">
+      <c r="E55" s="9">
         <v>1.01883723925276</v>
       </c>
-      <c r="F55" s="14">
+      <c r="F55" s="9">
         <v>2.2977437966203298</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="14">
+      <c r="C56" s="9">
         <v>0.86084187609014395</v>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="9">
         <v>2.2412879292675201</v>
       </c>
-      <c r="E56" s="14">
+      <c r="E56" s="9">
         <v>1.0324680061334299</v>
       </c>
-      <c r="F56" s="14">
+      <c r="F56" s="9">
         <v>0.55444443815425704</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="14">
+      <c r="C57" s="9">
         <v>0.76868617764432801</v>
       </c>
-      <c r="D57" s="14">
+      <c r="D57" s="9">
         <v>2.3099596563603</v>
       </c>
-      <c r="E57" s="14">
+      <c r="E57" s="9">
         <v>0.49941321414113299</v>
       </c>
-      <c r="F57" s="14">
+      <c r="F57" s="9">
         <v>0.22361110837742401</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="9">
         <v>0.21797121837481101</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D58" s="9">
         <v>1.7321562018168399</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E58" s="9">
         <v>0.43669332597479699</v>
       </c>
-      <c r="F58" s="14">
+      <c r="F58" s="9">
         <v>0.24674475530949</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="9">
         <v>-1.24395604635454</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D59" s="9">
         <v>1.5276388476826099</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E59" s="9">
         <v>3.9964482085831401</v>
       </c>
-      <c r="F59" s="14">
+      <c r="F59" s="9">
         <v>3.1179278061415499</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="14">
+      <c r="C60" s="9">
         <v>-0.83368440491295703</v>
       </c>
-      <c r="D60" s="14">
+      <c r="D60" s="9">
         <v>1.4164204256150399</v>
       </c>
-      <c r="E60" s="14">
+      <c r="E60" s="9">
         <v>4.04539959491684</v>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="9">
         <v>2.8143466392727601</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="14">
+      <c r="C61" s="9">
         <v>-0.39595846880292002</v>
       </c>
-      <c r="D61" s="14">
+      <c r="D61" s="9">
         <v>1.79533910848183</v>
       </c>
-      <c r="E61" s="14">
+      <c r="E61" s="9">
         <v>4.1544405551590504</v>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="9">
         <v>3.1996335626817398</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="14">
+      <c r="C62" s="9">
         <v>-7.4734534907920494E-2</v>
       </c>
-      <c r="D62" s="14">
+      <c r="D62" s="9">
         <v>2.4544510024086801</v>
       </c>
-      <c r="E62" s="14">
+      <c r="E62" s="9">
         <v>3.8955669295067601</v>
       </c>
-      <c r="F62" s="14">
+      <c r="F62" s="9">
         <v>3.23439585766892</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="14">
+      <c r="C63" s="9">
         <v>-0.39608151799060398</v>
       </c>
-      <c r="D63" s="14">
+      <c r="D63" s="9">
         <v>0.51198032878018696</v>
       </c>
-      <c r="E63" s="14">
+      <c r="E63" s="9">
         <v>1.4513447474524299</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="9">
         <v>4.00982103862661</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C64" s="14">
+      <c r="C64" s="9">
         <v>2.3600917554382899</v>
       </c>
-      <c r="D64" s="14">
+      <c r="D64" s="9">
         <v>-1.0359470041985599</v>
       </c>
-      <c r="E64" s="14">
+      <c r="E64" s="9">
         <v>3.0061668969144399</v>
       </c>
-      <c r="F64" s="14">
+      <c r="F64" s="9">
         <v>5.4511960029779196</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C65" s="14">
+      <c r="C65" s="9">
         <v>1.37132668996175</v>
       </c>
-      <c r="D65" s="14">
+      <c r="D65" s="9">
         <v>0.87034240426409104</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="9">
         <v>2.2928024799521198</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="9">
         <v>2.3185537811855998</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="10">
         <v>-1.4380893128974599</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="10">
         <v>0.92793453176222596</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="10">
         <v>2.0435243493659798</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="10">
         <v>3.08243353946385</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="10">
         <v>0.65081884044865002</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="10">
         <v>-0.45874527129686699</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="10">
         <v>1.6002819096992</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="10">
         <v>2.1398493746273299</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="10">
         <v>0.669832745749807</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="10">
         <v>0.74195656323181303</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="10">
         <v>0.86481279491544005</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="10">
         <v>1.86066952079766</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="10">
         <v>-0.70064269675413204</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="10">
         <v>0.93553913523727195</v>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="10">
         <v>1.10948299641873</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="10">
         <v>1.7915284223671399</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="10">
         <v>1.97256179331529E-2</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="10">
         <v>0.15042602065173899</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="10">
         <v>0.80839706484384999</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="10">
         <v>1.6575587608629101</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="10">
         <v>0.76380379971581902</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="10">
         <v>0.94716795711191304</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="10">
         <v>1.1167675274322599</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="10">
         <v>1.6132535278948601</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="16">
+      <c r="C72" s="10">
         <v>-0.58486004147984205</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="10">
         <v>1.1082553701787801</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="10">
         <v>2.0572634754929302</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="10">
         <v>1.98701949539025</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="10">
         <v>1.1046579478188501</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="10">
         <v>1.9857593494572301</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="10">
         <v>1.5809040232340701</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="10">
         <v>2.9217642823922998</v>
       </c>
     </row>
@@ -2312,4 +2308,1041 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694ED42F-0BB0-7740-B464-8FEDA9CF2C59}">
+  <dimension ref="A1:H73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>